--- a/pages/TP_demo.xlsx
+++ b/pages/TP_demo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samb\CNZPD\pages\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA17DEE9-BF31-4DC1-ADF0-32E9AB58A299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA1E8754-D662-40DD-9A8C-04CE6BDDC365}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11760" xr2:uid="{FF653D24-102F-4CF8-93AA-981FE732ABF2}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -429,7 +428,7 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="C2" t="s">
         <v>3</v>

--- a/pages/TP_demo.xlsx
+++ b/pages/TP_demo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samb\CNZPD\pages\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA1E8754-D662-40DD-9A8C-04CE6BDDC365}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29CE4497-DA04-4F85-A100-6914577C5311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11760" xr2:uid="{FF653D24-102F-4CF8-93AA-981FE732ABF2}"/>
+    <workbookView xWindow="28680" yWindow="-9135" windowWidth="29040" windowHeight="15990" xr2:uid="{FF653D24-102F-4CF8-93AA-981FE732ABF2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -406,13 +406,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48E42DB3-94C6-40E1-B231-4F22C1125ECF}">
-  <dimension ref="A1:C66"/>
+  <dimension ref="A1:E66"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -423,720 +424,785 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>0</v>
       </c>
-      <c r="B2">
-        <v>1.5</v>
+      <c r="B2" s="1">
+        <v>2.0848249731175459</v>
       </c>
       <c r="C2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E2" s="1"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>62.5</v>
       </c>
       <c r="B3" s="1">
-        <v>8.4400000000000546</v>
+        <v>8.8088024167206402</v>
       </c>
       <c r="C3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E3" s="1"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>125</v>
       </c>
       <c r="B4" s="1">
-        <v>13.180000000000055</v>
+        <v>13.243838784666435</v>
       </c>
       <c r="C4" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E4" s="1"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>187.5</v>
       </c>
       <c r="B5" s="1">
-        <v>17.300000000000061</v>
+        <v>17.911163538343899</v>
       </c>
       <c r="C5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E5" s="1"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>250</v>
       </c>
       <c r="B6" s="1">
-        <v>21.200000000000031</v>
+        <v>21.435143851690178</v>
       </c>
       <c r="C6" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E6" s="1"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>312.5</v>
       </c>
       <c r="B7" s="1">
-        <v>24.960000000000022</v>
+        <v>25.642552306286898</v>
       </c>
       <c r="C7" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E7" s="1"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>375</v>
       </c>
       <c r="B8" s="1">
-        <v>28.660000000000061</v>
+        <v>28.814616726922804</v>
       </c>
       <c r="C8" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E8" s="1"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>437.5</v>
       </c>
       <c r="B9" s="1">
-        <v>32.420000000000051</v>
+        <v>32.873681475302838</v>
       </c>
       <c r="C9" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E9" s="1"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>500</v>
       </c>
       <c r="B10" s="1">
-        <v>36.080000000000013</v>
+        <v>36.496648963716765</v>
       </c>
       <c r="C10" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E10" s="1"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>562.5</v>
       </c>
       <c r="B11" s="1">
-        <v>39.72</v>
+        <v>40.25442791045225</v>
       </c>
       <c r="C11" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E11" s="1"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>625</v>
       </c>
       <c r="B12" s="1">
-        <v>43.339999999999996</v>
+        <v>43.784883862755088</v>
       </c>
       <c r="C12" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E12" s="1"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>687.5</v>
       </c>
       <c r="B13" s="1">
-        <v>47.099999999999987</v>
+        <v>47.66899470862559</v>
       </c>
       <c r="C13" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E13" s="1"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>750</v>
       </c>
       <c r="B14" s="1">
-        <v>50.659999999999926</v>
+        <v>51.408907692756415</v>
       </c>
       <c r="C14" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E14" s="1"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>812.5</v>
       </c>
       <c r="B15" s="1">
-        <v>54.259999999999948</v>
+        <v>54.742718131470305</v>
       </c>
       <c r="C15" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E15" s="1"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>875</v>
       </c>
       <c r="B16" s="1">
-        <v>57.819999999999887</v>
+        <v>58.620254665666792</v>
       </c>
       <c r="C16" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E16" s="1"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>937.5</v>
       </c>
       <c r="B17" s="1">
-        <v>61.399999999999928</v>
+        <v>61.945514115143439</v>
       </c>
       <c r="C17" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E17" s="1"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>1000</v>
       </c>
       <c r="B18" s="1">
-        <v>64.919999999999902</v>
+        <v>65.707965115836288</v>
       </c>
       <c r="C18" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E18" s="1"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>1062.5</v>
       </c>
       <c r="B19" s="1">
-        <v>68.45999999999998</v>
+        <v>68.49921389770644</v>
       </c>
       <c r="C19" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E19" s="1"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>1125</v>
       </c>
       <c r="B20" s="1">
-        <v>72.000000000000057</v>
+        <v>72.366640588551235</v>
       </c>
       <c r="C20" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E20" s="1"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>1187.5</v>
       </c>
       <c r="B21" s="1">
-        <v>75.660000000000025</v>
+        <v>76.067881248819205</v>
       </c>
       <c r="C21" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E21" s="1"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>1250</v>
       </c>
       <c r="B22" s="1">
-        <v>79.199999999999989</v>
+        <v>80.087863154708685</v>
       </c>
       <c r="C22" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E22" s="1"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>1312.5</v>
       </c>
       <c r="B23" s="1">
-        <v>82.739999999999952</v>
+        <v>83.110461033676103</v>
       </c>
       <c r="C23" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E23" s="1"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>1375</v>
       </c>
       <c r="B24" s="1">
-        <v>86.239999999999952</v>
+        <v>86.556205588836207</v>
       </c>
       <c r="C24" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E24" s="1"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>1437.5</v>
       </c>
       <c r="B25" s="1">
-        <v>89.759999999999934</v>
+        <v>90.514896003823267</v>
       </c>
       <c r="C25" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E25" s="1"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>1500</v>
       </c>
       <c r="B26" s="1">
-        <v>93.299999999999898</v>
+        <v>93.90930074417318</v>
       </c>
       <c r="C26" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E26" s="1"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>1562.5</v>
       </c>
       <c r="B27" s="1">
-        <v>96.859999999999957</v>
+        <v>97.333791111615753</v>
       </c>
       <c r="C27" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E27" s="1"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>1625</v>
       </c>
       <c r="B28" s="1">
-        <v>100.4199999999999</v>
+        <v>100.43646292987485</v>
       </c>
       <c r="C28" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E28" s="1"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>1687.5</v>
       </c>
       <c r="B29" s="1">
-        <v>103.99999999999994</v>
+        <v>104.3507566530749</v>
       </c>
       <c r="C29" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E29" s="1"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>1750</v>
       </c>
       <c r="B30" s="1">
-        <v>107.57999999999998</v>
+        <v>108.12117554646339</v>
       </c>
       <c r="C30" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E30" s="1"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>1812.5</v>
       </c>
       <c r="B31" s="1">
-        <v>111.30000000000001</v>
+        <v>112.12071793055979</v>
       </c>
       <c r="C31" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E31" s="1"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>1875</v>
       </c>
       <c r="B32" s="1">
-        <v>114.89999999999991</v>
+        <v>115.7563518533011</v>
       </c>
       <c r="C32" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E32" s="1"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>1937.5</v>
       </c>
       <c r="B33" s="1">
-        <v>118.51999999999991</v>
+        <v>119.01543732053885</v>
       </c>
       <c r="C33" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E33" s="1"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>2000</v>
       </c>
       <c r="B34" s="1">
-        <v>122.11999999999981</v>
+        <v>122.60910267726025</v>
       </c>
       <c r="C34" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E34" s="1"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>2062.5</v>
       </c>
       <c r="B35" s="1">
-        <v>125.75999999999991</v>
+        <v>126.00752866096499</v>
       </c>
       <c r="C35" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E35" s="1"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>2125</v>
       </c>
       <c r="B36" s="1">
-        <v>129.4</v>
+        <v>129.65435044956757</v>
       </c>
       <c r="C36" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E36" s="1"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>2187.5</v>
       </c>
       <c r="B37" s="1">
-        <v>133.04</v>
+        <v>133.69112578844135</v>
       </c>
       <c r="C37" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E37" s="1"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>2250</v>
       </c>
       <c r="B38" s="1">
-        <v>136.73999999999992</v>
+        <v>136.89901443789793</v>
       </c>
       <c r="C38" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E38" s="1"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>2312.5</v>
       </c>
       <c r="B39" s="1">
-        <v>140.5199999999999</v>
+        <v>140.96863905074289</v>
       </c>
       <c r="C39" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E39" s="1"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>2375</v>
       </c>
       <c r="B40" s="1">
-        <v>144.25999999999991</v>
+        <v>144.70619191785912</v>
       </c>
       <c r="C40" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E40" s="1"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>2437.5</v>
       </c>
       <c r="B41" s="1">
-        <v>148.11999999999992</v>
+        <v>148.47928472345245</v>
       </c>
       <c r="C41" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E41" s="1"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>2500</v>
       </c>
       <c r="B42" s="1">
-        <v>151.79999999999987</v>
+        <v>152.30300330256819</v>
       </c>
       <c r="C42" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E42" s="1"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>2562.5</v>
       </c>
       <c r="B43" s="1">
-        <v>155.47999999999993</v>
+        <v>155.75684535045366</v>
       </c>
       <c r="C43" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E43" s="1"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>2625</v>
       </c>
       <c r="B44" s="1">
-        <v>159.1399999999999</v>
+        <v>159.5216839043733</v>
       </c>
       <c r="C44" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E44" s="1"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>2687.5</v>
       </c>
       <c r="B45" s="1">
-        <v>162.81999999999996</v>
+        <v>163.43024435003059</v>
       </c>
       <c r="C45" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E45" s="1"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>2750</v>
       </c>
       <c r="B46" s="1">
-        <v>166.42</v>
+        <v>166.98241245445431</v>
       </c>
       <c r="C46" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E46" s="1"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>2812.5</v>
       </c>
       <c r="B47" s="1">
-        <v>170.05999999999997</v>
+        <v>170.0739102426179</v>
       </c>
       <c r="C47" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E47" s="1"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>2875</v>
       </c>
       <c r="B48" s="1">
-        <v>173.67999999999986</v>
+        <v>173.82354247449251</v>
       </c>
       <c r="C48" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E48" s="1"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>2937.5</v>
       </c>
       <c r="B49" s="1">
-        <v>177.39999999999989</v>
+        <v>177.43606368160127</v>
       </c>
       <c r="C49" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E49" s="1"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>3000</v>
       </c>
       <c r="B50" s="1">
-        <v>180.95999999999995</v>
+        <v>181.41076354726835</v>
       </c>
       <c r="C50" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E50" s="1"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>3062.5</v>
       </c>
       <c r="B51" s="1">
-        <v>184.55999999999997</v>
+        <v>185.39276439292794</v>
       </c>
       <c r="C51" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E51" s="1"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>3125</v>
       </c>
       <c r="B52" s="1">
-        <v>188.11999999999992</v>
+        <v>188.79521094971119</v>
       </c>
       <c r="C52" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E52" s="1"/>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>3187.5</v>
       </c>
       <c r="B53" s="1">
-        <v>191.71999999999994</v>
+        <v>192.02018918095123</v>
       </c>
       <c r="C53" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E53" s="1"/>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>3250</v>
       </c>
       <c r="B54" s="1">
-        <v>195.27999999999989</v>
+        <v>196.09082298559488</v>
       </c>
       <c r="C54" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E54" s="1"/>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>3312.5</v>
       </c>
       <c r="B55" s="1">
-        <v>198.85999999999993</v>
+        <v>199.0966657853343</v>
       </c>
       <c r="C55" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E55" s="1"/>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>3375</v>
       </c>
       <c r="B56" s="1">
-        <v>202.45999999999995</v>
+        <v>202.63814801891365</v>
       </c>
       <c r="C56" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E56" s="1"/>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>3437.5</v>
       </c>
       <c r="B57" s="1">
-        <v>206.05999999999997</v>
+        <v>206.47654673757862</v>
       </c>
       <c r="C57" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E57" s="1"/>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>3500</v>
       </c>
       <c r="B58" s="1">
-        <v>209.71999999999983</v>
+        <v>210.04264653063592</v>
       </c>
       <c r="C58" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E58" s="1"/>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>3562.5</v>
       </c>
       <c r="B59" s="1">
-        <v>213.43999999999986</v>
+        <v>213.50990941028218</v>
       </c>
       <c r="C59" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E59" s="1"/>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>3625</v>
       </c>
       <c r="B60" s="1">
-        <v>217.11999999999992</v>
+        <v>217.63746986541256</v>
       </c>
       <c r="C60" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E60" s="1"/>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>3687.5</v>
       </c>
       <c r="B61" s="1">
-        <v>220.79999999999998</v>
+        <v>221.44495001780601</v>
       </c>
       <c r="C61" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E61" s="1"/>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>3750</v>
       </c>
       <c r="B62" s="1">
-        <v>224.4999999999998</v>
+        <v>225.3615901284422</v>
       </c>
       <c r="C62" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E62" s="1"/>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>3812.5</v>
       </c>
       <c r="B63" s="1">
-        <v>228.19999999999985</v>
+        <v>229.15286655370156</v>
       </c>
       <c r="C63" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E63" s="1"/>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>3875</v>
       </c>
       <c r="B64" s="1">
-        <v>231.91999999999987</v>
+        <v>232.66230700361064</v>
       </c>
       <c r="C64" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E64" s="1"/>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>3937.5</v>
       </c>
       <c r="B65" s="1">
-        <v>235.65999999999988</v>
+        <v>236.6403943219307</v>
       </c>
       <c r="C65" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E65" s="1"/>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>4000</v>
       </c>
       <c r="B66" s="1">
-        <v>239.59999999999994</v>
+        <v>239.88201895827308</v>
       </c>
       <c r="C66" t="s">
         <v>3</v>
       </c>
+      <c r="E66" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
